--- a/data/daily_work.xlsx
+++ b/data/daily_work.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pending Review</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -517,6 +517,123 @@
       <c r="J2" t="n">
         <v>12</v>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Adding the employee details</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Changes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Now make it complete
+</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10:58 AM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Dadhboard</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>working on leave request</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>11:56 AM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dadhboard</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Submint work section done</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01:27 PM</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Dadhboard</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/daily_work.xlsx
+++ b/data/daily_work.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>emp_id</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -446,194 +446,24 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>emp_id</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>admin_review</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>02:31 PM</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>santparampra.in</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Adding the employee details</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Changes</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Now make it complete
-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>10:58 AM</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Dadhboard</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>working on leave request</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>11:56 AM</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Dadhboard</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Submint work section done</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>01:27 PM</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Dadhboard</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/daily_work.xlsx
+++ b/data/daily_work.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,53 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RV002</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>05:03 PM</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>santparampra.in</t>
         </is>
       </c>
     </row>
